--- a/scripts/.tmp/rendicion-transf-test.xlsx
+++ b/scripts/.tmp/rendicion-transf-test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esteb\Documents\proyecto_cursor\proyectoisaqwenvisor\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90075A0A-0C6D-49CB-A4E0-D1F4E8A05D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5A2FE6-1569-4076-B559-FA7ED3CBDF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="107">
   <si>
     <t>RECORRIDO</t>
   </si>
@@ -261,18 +261,9 @@
     <t>{{extraction.total_n_c_por_negocios.valor}}</t>
   </si>
   <si>
-    <t>{{extraction.auxiliar.valor}}</t>
-  </si>
-  <si>
-    <t>{{extraction.conductor.valor}}</t>
-  </si>
-  <si>
     <t>{{extraction.cant_fact.valor}}</t>
   </si>
   <si>
-    <t>{{extraction.n_recorrido.valor}}</t>
-  </si>
-  <si>
     <t>{{extraction.valor_total.valor}}</t>
   </si>
   <si>
@@ -334,6 +325,36 @@
   </si>
   <si>
     <t>{{transf_banco}}</t>
+  </si>
+  <si>
+    <t>{{chq_dia_fechas}}</t>
+  </si>
+  <si>
+    <t>{{chq_dia_bancos}}</t>
+  </si>
+  <si>
+    <t>{{chq_dia_valores}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.conductor}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.auxiliar}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.observaciones}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.sector}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.recorrido}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.n_factura}}</t>
+  </si>
+  <si>
+    <t>{{extraction._meta.bitacora.excel.total_factura}}</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1032,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="230">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1452,6 +1473,94 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="18" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="18" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="6" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1460,25 +1569,16 @@
     <xf numFmtId="42" fontId="6" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1487,36 +1587,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1529,92 +1599,52 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1958,7 +1988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W113"/>
+  <dimension ref="A1:W112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.33203125" customWidth="1"/>
@@ -1985,7 +2015,9 @@
       <c r="A1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="127"/>
+      <c r="B1" s="127" t="s">
+        <v>100</v>
+      </c>
       <c r="C1" s="143"/>
       <c r="D1" s="143"/>
       <c r="E1" s="127"/>
@@ -2012,7 +2044,9 @@
       <c r="A2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="127"/>
+      <c r="B2" s="127" t="s">
+        <v>101</v>
+      </c>
       <c r="C2" s="143"/>
       <c r="D2" s="143"/>
       <c r="E2" s="127"/>
@@ -2039,7 +2073,9 @@
       <c r="A3" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="143"/>
+      <c r="B3" s="143" t="s">
+        <v>102</v>
+      </c>
       <c r="C3" s="143"/>
       <c r="D3" s="143"/>
       <c r="E3" s="143"/>
@@ -2066,7 +2102,9 @@
       <c r="A4" s="146" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="143"/>
+      <c r="B4" s="143" t="s">
+        <v>103</v>
+      </c>
       <c r="C4" s="143"/>
       <c r="D4" s="143"/>
       <c r="E4" s="143"/>
@@ -2093,10 +2131,8 @@
       <c r="A5" s="127" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">99999</t>
-        </is>
+      <c r="B5" s="154" t="s">
+        <v>104</v>
       </c>
       <c r="C5" s="154"/>
       <c r="D5" s="154"/>
@@ -2124,7 +2160,9 @@
       <c r="A6" s="127" t="s">
         <v>1</v>
       </c>
-      <c r="B6"/>
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6"/>
@@ -2147,11 +2185,13 @@
       <c r="V6" s="123"/>
       <c r="W6" s="123"/>
     </row>
-    <row r="7" spans="1:23" s="49" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" s="49" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="155"/>
+      <c r="B7" s="155" t="s">
+        <v>106</v>
+      </c>
       <c r="C7" s="155"/>
       <c r="D7" s="155"/>
       <c r="E7" s="155"/>
@@ -2680,17 +2720,17 @@
     </row>
     <row r="22" spans="1:23" s="1" customFormat="1" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="2"/>
-      <c r="M22" s="174" t="s">
+      <c r="M22" s="215" t="s">
         <v>48</v>
       </c>
-      <c r="N22" s="174"/>
-      <c r="O22" s="174"/>
-      <c r="P22" s="174"/>
-      <c r="Q22" s="174"/>
-      <c r="R22" s="174"/>
-      <c r="S22" s="174"/>
-      <c r="T22" s="174"/>
-      <c r="U22" s="174"/>
+      <c r="N22" s="215"/>
+      <c r="O22" s="215"/>
+      <c r="P22" s="215"/>
+      <c r="Q22" s="215"/>
+      <c r="R22" s="215"/>
+      <c r="S22" s="215"/>
+      <c r="T22" s="215"/>
+      <c r="U22" s="215"/>
     </row>
     <row r="23" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D23" s="6"/>
@@ -2699,12 +2739,12 @@
       <c r="M23" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="N23" s="185"/>
-      <c r="O23" s="186"/>
-      <c r="P23" s="186"/>
-      <c r="Q23" s="186"/>
-      <c r="R23" s="186"/>
-      <c r="S23" s="187"/>
+      <c r="N23" s="222"/>
+      <c r="O23" s="223"/>
+      <c r="P23" s="223"/>
+      <c r="Q23" s="223"/>
+      <c r="R23" s="223"/>
+      <c r="S23" s="224"/>
       <c r="T23" s="142" t="s">
         <v>38</v>
       </c>
@@ -2720,21 +2760,19 @@
       <c r="K24" s="15"/>
       <c r="L24"/>
       <c r="M24" s="16"/>
-      <c r="N24" s="188" t="s">
+      <c r="N24" s="225" t="s">
         <v>49</v>
       </c>
-      <c r="O24" s="189"/>
-      <c r="P24" s="189"/>
-      <c r="Q24" s="189"/>
-      <c r="R24" s="189"/>
-      <c r="S24" s="190"/>
+      <c r="O24" s="226"/>
+      <c r="P24" s="226"/>
+      <c r="Q24" s="226"/>
+      <c r="R24" s="226"/>
+      <c r="S24" s="227"/>
       <c r="T24" s="117" t="s">
         <v>11</v>
       </c>
       <c r="U24" s="116"/>
-      <c r="W24" s="141" t="str">
-        <f>U23</f>
-      </c>
+      <c r="W24" s="141"/>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="B25" s="2"/>
@@ -2745,19 +2783,19 @@
       <c r="E25" s="4"/>
       <c r="J25"/>
       <c r="L25"/>
-      <c r="M25" s="193" t="s">
+      <c r="M25" s="210" t="s">
         <v>16</v>
       </c>
-      <c r="N25" s="194"/>
-      <c r="O25" s="195"/>
-      <c r="P25" s="196"/>
-      <c r="Q25" s="171"/>
-      <c r="R25" s="172"/>
-      <c r="S25" s="173"/>
-      <c r="T25" s="191" t="s">
+      <c r="N25" s="211"/>
+      <c r="O25" s="212"/>
+      <c r="P25" s="213"/>
+      <c r="Q25" s="201"/>
+      <c r="R25" s="202"/>
+      <c r="S25" s="203"/>
+      <c r="T25" s="228" t="s">
         <v>17</v>
       </c>
-      <c r="U25" s="192"/>
+      <c r="U25" s="229"/>
       <c r="V25" s="13"/>
       <c r="W25" s="86" t="s">
         <v>45</v>
@@ -2773,9 +2811,9 @@
       <c r="N26" s="84"/>
       <c r="O26" s="151"/>
       <c r="P26" s="152"/>
-      <c r="Q26" s="171"/>
-      <c r="R26" s="172"/>
-      <c r="S26" s="173"/>
+      <c r="Q26" s="201"/>
+      <c r="R26" s="202"/>
+      <c r="S26" s="203"/>
       <c r="T26" s="149"/>
       <c r="U26" s="150"/>
       <c r="V26" s="13"/>
@@ -2793,19 +2831,17 @@
         <v>18</v>
       </c>
       <c r="N27" s="84"/>
-      <c r="O27" s="175"/>
-      <c r="P27" s="176"/>
-      <c r="Q27" s="171"/>
-      <c r="R27" s="172"/>
-      <c r="S27" s="173"/>
-      <c r="T27" s="183" t="s">
+      <c r="O27" s="194"/>
+      <c r="P27" s="195"/>
+      <c r="Q27" s="201"/>
+      <c r="R27" s="202"/>
+      <c r="S27" s="203"/>
+      <c r="T27" s="220" t="s">
         <v>19</v>
       </c>
-      <c r="U27" s="184"/>
+      <c r="U27" s="221"/>
       <c r="V27" s="19"/>
-      <c r="W27" s="97" t="str">
-        <f>U24</f>
-      </c>
+      <c r="W27" s="97"/>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="I28" s="118">
@@ -2817,19 +2853,19 @@
         <v>0</v>
       </c>
       <c r="L28"/>
-      <c r="M28" s="181" t="s">
+      <c r="M28" s="208" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="182"/>
-      <c r="O28" s="175"/>
-      <c r="P28" s="176"/>
-      <c r="Q28" s="171"/>
-      <c r="R28" s="172"/>
-      <c r="S28" s="173"/>
-      <c r="T28" s="179" t="s">
+      <c r="N28" s="209"/>
+      <c r="O28" s="194"/>
+      <c r="P28" s="195"/>
+      <c r="Q28" s="201"/>
+      <c r="R28" s="202"/>
+      <c r="S28" s="203"/>
+      <c r="T28" s="218" t="s">
         <v>39</v>
       </c>
-      <c r="U28" s="180"/>
+      <c r="U28" s="219"/>
       <c r="V28" s="21"/>
       <c r="W28" s="13"/>
     </row>
@@ -2844,19 +2880,19 @@
       </c>
       <c r="K29" s="24"/>
       <c r="L29"/>
-      <c r="M29" s="181" t="s">
+      <c r="M29" s="208" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="182"/>
-      <c r="O29" s="175"/>
-      <c r="P29" s="176"/>
-      <c r="Q29" s="171"/>
-      <c r="R29" s="172"/>
-      <c r="S29" s="173"/>
-      <c r="T29" s="177" t="s">
+      <c r="N29" s="209"/>
+      <c r="O29" s="194"/>
+      <c r="P29" s="195"/>
+      <c r="Q29" s="201"/>
+      <c r="R29" s="202"/>
+      <c r="S29" s="203"/>
+      <c r="T29" s="216" t="s">
         <v>40</v>
       </c>
-      <c r="U29" s="178"/>
+      <c r="U29" s="217"/>
       <c r="W29" s="98" t="str">
         <f>U23</f>
       </c>
@@ -2872,19 +2908,19 @@
         <v>0</v>
       </c>
       <c r="L30"/>
-      <c r="M30" s="181" t="s">
+      <c r="M30" s="208" t="s">
         <v>22</v>
       </c>
-      <c r="N30" s="182"/>
-      <c r="O30" s="175"/>
-      <c r="P30" s="203"/>
-      <c r="Q30" s="171"/>
-      <c r="R30" s="172"/>
-      <c r="S30" s="173"/>
-      <c r="T30" s="204" t="s">
+      <c r="N30" s="209"/>
+      <c r="O30" s="194"/>
+      <c r="P30" s="214"/>
+      <c r="Q30" s="201"/>
+      <c r="R30" s="202"/>
+      <c r="S30" s="203"/>
+      <c r="T30" s="199" t="s">
         <v>41</v>
       </c>
-      <c r="U30" s="205"/>
+      <c r="U30" s="200"/>
       <c r="V30" s="24"/>
       <c r="W30" s="21" t="str">
         <f>Q34</f>
@@ -2901,15 +2937,15 @@
         <v>0</v>
       </c>
       <c r="L31"/>
-      <c r="M31" s="181" t="s">
+      <c r="M31" s="208" t="s">
         <v>23</v>
       </c>
-      <c r="N31" s="182"/>
-      <c r="O31" s="175"/>
-      <c r="P31" s="176"/>
-      <c r="Q31" s="171"/>
-      <c r="R31" s="172"/>
-      <c r="S31" s="173"/>
+      <c r="N31" s="209"/>
+      <c r="O31" s="194"/>
+      <c r="P31" s="195"/>
+      <c r="Q31" s="201"/>
+      <c r="R31" s="202"/>
+      <c r="S31" s="203"/>
       <c r="T31" s="28"/>
       <c r="U31" s="26"/>
     </row>
@@ -2924,15 +2960,15 @@
         <v>0</v>
       </c>
       <c r="L32"/>
-      <c r="M32" s="181" t="s">
+      <c r="M32" s="208" t="s">
         <v>24</v>
       </c>
-      <c r="N32" s="182"/>
-      <c r="O32" s="175"/>
-      <c r="P32" s="176"/>
-      <c r="Q32" s="171"/>
-      <c r="R32" s="172"/>
-      <c r="S32" s="173"/>
+      <c r="N32" s="209"/>
+      <c r="O32" s="194"/>
+      <c r="P32" s="195"/>
+      <c r="Q32" s="201"/>
+      <c r="R32" s="202"/>
+      <c r="S32" s="203"/>
       <c r="T32" s="28"/>
       <c r="U32" s="26"/>
       <c r="W32" s="86" t="s">
@@ -2954,11 +2990,11 @@
         <v>25</v>
       </c>
       <c r="N33" s="85"/>
-      <c r="O33" s="175"/>
-      <c r="P33" s="176"/>
-      <c r="Q33" s="171"/>
-      <c r="R33" s="172"/>
-      <c r="S33" s="173"/>
+      <c r="O33" s="194"/>
+      <c r="P33" s="195"/>
+      <c r="Q33" s="201"/>
+      <c r="R33" s="202"/>
+      <c r="S33" s="203"/>
       <c r="T33" s="28"/>
       <c r="U33" s="26"/>
       <c r="W33" s="138" t="e">
@@ -2977,15 +3013,15 @@
         <v>0</v>
       </c>
       <c r="L34" s="8"/>
-      <c r="M34" s="199" t="s">
+      <c r="M34" s="204" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="200"/>
-      <c r="O34" s="201"/>
-      <c r="P34" s="202"/>
-      <c r="Q34" s="171"/>
-      <c r="R34" s="172"/>
-      <c r="S34" s="173"/>
+      <c r="N34" s="205"/>
+      <c r="O34" s="206"/>
+      <c r="P34" s="207"/>
+      <c r="Q34" s="201"/>
+      <c r="R34" s="202"/>
+      <c r="S34" s="203"/>
       <c r="T34" s="30"/>
       <c r="U34" s="29"/>
       <c r="V34" s="1"/>
@@ -3003,23 +3039,23 @@
         <v>0</v>
       </c>
       <c r="L35"/>
-      <c r="M35" s="209" t="s">
+      <c r="M35" s="191" t="s">
         <v>27</v>
       </c>
-      <c r="N35" s="210"/>
-      <c r="O35" s="211"/>
-      <c r="P35" s="197" t="s">
+      <c r="N35" s="192"/>
+      <c r="O35" s="193"/>
+      <c r="P35" s="186" t="s">
         <v>28</v>
       </c>
-      <c r="Q35" s="198"/>
-      <c r="R35" s="197" t="s">
+      <c r="Q35" s="190"/>
+      <c r="R35" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="S35" s="198"/>
-      <c r="T35" s="197" t="s">
+      <c r="S35" s="190"/>
+      <c r="T35" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="U35" s="198"/>
+      <c r="U35" s="190"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
     </row>
@@ -3101,10 +3137,10 @@
       <c r="L38" s="114">
         <v>2</v>
       </c>
-      <c r="M38" s="207" t="s">
+      <c r="M38" s="180" t="s">
         <v>42</v>
       </c>
-      <c r="N38" s="208"/>
+      <c r="N38" s="181"/>
       <c r="O38" s="46"/>
       <c r="P38" s="42"/>
       <c r="Q38" s="79"/>
@@ -3212,8 +3248,8 @@
       <c r="A43" s="112"/>
       <c r="B43" s="20"/>
       <c r="C43" s="32"/>
-      <c r="D43" s="206"/>
-      <c r="E43" s="206"/>
+      <c r="D43" s="174"/>
+      <c r="E43" s="174"/>
       <c r="F43" s="51"/>
       <c r="G43" s="8"/>
       <c r="I43" s="136"/>
@@ -3239,8 +3275,8 @@
       <c r="A44" s="25"/>
       <c r="B44" s="20"/>
       <c r="C44" s="25"/>
-      <c r="D44" s="206"/>
-      <c r="E44" s="206"/>
+      <c r="D44" s="174"/>
+      <c r="E44" s="174"/>
       <c r="F44" s="52"/>
       <c r="H44" s="68"/>
       <c r="I44" s="13"/>
@@ -3263,8 +3299,8 @@
       <c r="A45" s="25"/>
       <c r="B45" s="25"/>
       <c r="C45" s="43"/>
-      <c r="D45" s="206"/>
-      <c r="E45" s="206"/>
+      <c r="D45" s="174"/>
+      <c r="E45" s="174"/>
       <c r="F45" s="23"/>
       <c r="H45" s="68"/>
       <c r="I45" s="13"/>
@@ -3286,8 +3322,8 @@
       <c r="A46" s="20"/>
       <c r="B46" s="20"/>
       <c r="C46" s="43"/>
-      <c r="D46" s="206"/>
-      <c r="E46" s="206"/>
+      <c r="D46" s="174"/>
+      <c r="E46" s="174"/>
       <c r="F46" s="53"/>
       <c r="H46" s="68"/>
       <c r="I46" s="13"/>
@@ -3309,8 +3345,8 @@
       <c r="A47" s="20"/>
       <c r="B47" s="20"/>
       <c r="C47" s="43"/>
-      <c r="D47" s="206"/>
-      <c r="E47" s="206"/>
+      <c r="D47" s="174"/>
+      <c r="E47" s="174"/>
       <c r="F47" s="17"/>
       <c r="G47" s="1"/>
       <c r="H47" s="68"/>
@@ -3337,8 +3373,8 @@
       <c r="A48" s="20"/>
       <c r="B48" s="20"/>
       <c r="C48" s="43"/>
-      <c r="D48" s="206"/>
-      <c r="E48" s="206"/>
+      <c r="D48" s="174"/>
+      <c r="E48" s="174"/>
       <c r="F48" s="23"/>
       <c r="G48" s="1"/>
       <c r="H48" s="68"/>
@@ -3361,8 +3397,8 @@
       <c r="A49" s="20"/>
       <c r="B49" s="20"/>
       <c r="C49" s="43"/>
-      <c r="D49" s="206"/>
-      <c r="E49" s="206"/>
+      <c r="D49" s="174"/>
+      <c r="E49" s="174"/>
       <c r="F49" s="23"/>
       <c r="G49" s="1"/>
       <c r="H49" s="50"/>
@@ -3409,8 +3445,8 @@
       <c r="A51" s="20"/>
       <c r="B51" s="20"/>
       <c r="C51" s="43"/>
-      <c r="D51" s="220"/>
-      <c r="E51" s="220"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
       <c r="F51" s="23"/>
       <c r="G51" s="1"/>
       <c r="H51" s="50"/>
@@ -3433,8 +3469,8 @@
       <c r="A52" s="20"/>
       <c r="B52" s="55"/>
       <c r="C52" s="43"/>
-      <c r="D52" s="221"/>
-      <c r="E52" s="221"/>
+      <c r="D52" s="183"/>
+      <c r="E52" s="183"/>
       <c r="F52" s="23"/>
       <c r="G52" s="1"/>
       <c r="H52" s="50"/>
@@ -3457,8 +3493,8 @@
       <c r="A53" s="25"/>
       <c r="B53" s="55"/>
       <c r="C53" s="43"/>
-      <c r="D53" s="217"/>
-      <c r="E53" s="217"/>
+      <c r="D53" s="182"/>
+      <c r="E53" s="182"/>
       <c r="F53" s="23"/>
       <c r="G53" s="1"/>
       <c r="H53" s="50"/>
@@ -3479,8 +3515,8 @@
       <c r="A54" s="20"/>
       <c r="B54" s="55"/>
       <c r="C54" s="43"/>
-      <c r="D54" s="217"/>
-      <c r="E54" s="217"/>
+      <c r="D54" s="182"/>
+      <c r="E54" s="182"/>
       <c r="F54" s="23"/>
       <c r="G54" s="1"/>
       <c r="H54" s="50"/>
@@ -3611,8 +3647,8 @@
       <c r="A60" s="25"/>
       <c r="B60"/>
       <c r="C60" s="43"/>
-      <c r="D60" s="217"/>
-      <c r="E60" s="217"/>
+      <c r="D60" s="182"/>
+      <c r="E60" s="182"/>
       <c r="F60" s="23"/>
       <c r="G60" s="1"/>
       <c r="H60" s="50"/>
@@ -3699,8 +3735,8 @@
       <c r="A64" s="25"/>
       <c r="B64"/>
       <c r="C64" s="43"/>
-      <c r="D64" s="217"/>
-      <c r="E64" s="217"/>
+      <c r="D64" s="182"/>
+      <c r="E64" s="182"/>
       <c r="F64" s="23"/>
       <c r="G64" s="1"/>
       <c r="H64" s="50"/>
@@ -3721,18 +3757,18 @@
       <c r="A65" s="25"/>
       <c r="B65"/>
       <c r="C65" s="43"/>
-      <c r="D65" s="217"/>
-      <c r="E65" s="217"/>
+      <c r="D65" s="182"/>
+      <c r="E65" s="182"/>
       <c r="F65" s="20"/>
       <c r="G65" s="1"/>
       <c r="H65" s="50"/>
       <c r="I65" s="54"/>
       <c r="J65" s="57"/>
       <c r="L65"/>
-      <c r="M65" s="207" t="s">
+      <c r="M65" s="180" t="s">
         <v>34</v>
       </c>
-      <c r="N65" s="208"/>
+      <c r="N65" s="181"/>
       <c r="O65" s="46"/>
       <c r="P65" s="56" t="s">
         <v>11</v>
@@ -3751,8 +3787,8 @@
       <c r="A66" s="25"/>
       <c r="B66"/>
       <c r="C66" s="95"/>
-      <c r="D66" s="217"/>
-      <c r="E66" s="217"/>
+      <c r="D66" s="182"/>
+      <c r="E66" s="182"/>
       <c r="F66" s="23"/>
       <c r="G66" s="1"/>
       <c r="H66" s="50"/>
@@ -3780,28 +3816,28 @@
       <c r="I67" s="54"/>
       <c r="J67"/>
       <c r="L67"/>
-      <c r="M67" s="197" t="s">
+      <c r="M67" s="186" t="s">
         <v>47</v>
       </c>
-      <c r="N67" s="216"/>
-      <c r="O67" s="198"/>
-      <c r="P67" s="218"/>
-      <c r="Q67" s="219"/>
-      <c r="R67" s="197" t="s">
+      <c r="N67" s="187"/>
+      <c r="O67" s="190"/>
+      <c r="P67" s="188"/>
+      <c r="Q67" s="189"/>
+      <c r="R67" s="186" t="s">
         <v>37</v>
       </c>
-      <c r="S67" s="216"/>
-      <c r="T67" s="212" t="str">
+      <c r="S67" s="187"/>
+      <c r="T67" s="196" t="str">
         <f>Q25</f>
       </c>
-      <c r="U67" s="213"/>
+      <c r="U67" s="197"/>
     </row>
     <row r="68" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="25"/>
       <c r="B68"/>
       <c r="C68" s="25"/>
-      <c r="D68" s="217"/>
-      <c r="E68" s="217"/>
+      <c r="D68" s="182"/>
+      <c r="E68" s="182"/>
       <c r="F68" s="67"/>
       <c r="G68" s="1"/>
       <c r="H68" s="50"/>
@@ -3822,33 +3858,33 @@
       <c r="A69" s="25"/>
       <c r="B69" s="95"/>
       <c r="C69" s="25"/>
-      <c r="D69" s="217"/>
-      <c r="E69" s="217"/>
+      <c r="D69" s="182"/>
+      <c r="E69" s="182"/>
       <c r="F69" s="67"/>
       <c r="G69" s="1"/>
       <c r="H69" s="50"/>
       <c r="I69" s="54"/>
       <c r="J69"/>
       <c r="L69"/>
-      <c r="M69" s="207" t="s">
+      <c r="M69" s="180" t="s">
         <v>35</v>
       </c>
-      <c r="N69" s="214"/>
-      <c r="O69" s="214"/>
-      <c r="P69" s="214"/>
-      <c r="Q69" s="214"/>
-      <c r="R69" s="214"/>
-      <c r="S69" s="214"/>
-      <c r="T69" s="214"/>
-      <c r="U69" s="215"/>
+      <c r="N69" s="184"/>
+      <c r="O69" s="184"/>
+      <c r="P69" s="184"/>
+      <c r="Q69" s="184"/>
+      <c r="R69" s="184"/>
+      <c r="S69" s="184"/>
+      <c r="T69" s="184"/>
+      <c r="U69" s="185"/>
       <c r="V69" s="55"/>
     </row>
     <row r="70" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="25"/>
       <c r="B70" s="20"/>
       <c r="C70" s="25"/>
-      <c r="D70" s="217"/>
-      <c r="E70" s="217"/>
+      <c r="D70" s="182"/>
+      <c r="E70" s="182"/>
       <c r="F70" s="67"/>
       <c r="G70" s="1"/>
       <c r="H70" s="50"/>
@@ -3885,8 +3921,8 @@
       <c r="A71" s="25"/>
       <c r="B71" s="130"/>
       <c r="C71" s="25"/>
-      <c r="D71" s="217"/>
-      <c r="E71" s="217"/>
+      <c r="D71" s="182"/>
+      <c r="E71" s="182"/>
       <c r="F71" s="67"/>
       <c r="G71" s="1"/>
       <c r="H71" s="50"/>
@@ -3900,10 +3936,10 @@
       </c>
       <c r="P71" s="66"/>
       <c r="Q71" s="65"/>
-      <c r="R71" s="226" t="s">
+      <c r="R71" s="179" t="s">
         <v>6</v>
       </c>
-      <c r="S71" s="226"/>
+      <c r="S71" s="179"/>
       <c r="T71" s="159"/>
       <c r="U71" s="160"/>
       <c r="V71" s="55"/>
@@ -3911,8 +3947,8 @@
     <row r="72" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B72" s="55"/>
       <c r="C72" s="94"/>
-      <c r="D72" s="217"/>
-      <c r="E72" s="217"/>
+      <c r="D72" s="182"/>
+      <c r="E72" s="182"/>
       <c r="F72" s="67"/>
       <c r="I72" s="130"/>
       <c r="L72"/>
@@ -3921,8 +3957,8 @@
       <c r="O72" s="18"/>
       <c r="P72" s="91"/>
       <c r="Q72" s="60"/>
-      <c r="R72" s="224"/>
-      <c r="S72" s="224"/>
+      <c r="R72" s="177"/>
+      <c r="S72" s="177"/>
       <c r="T72" s="69"/>
       <c r="U72" s="100"/>
       <c r="V72" s="55"/>
@@ -3955,132 +3991,129 @@
         </is>
       </c>
       <c r="Q73" s="60"/>
-      <c r="R73" s="224" t="s">
+      <c r="R73" s="177" t="s">
         <v>10</v>
       </c>
-      <c r="S73" s="224"/>
+      <c r="S73" s="177"/>
       <c r="T73" s="69">
         <v>150000</v>
       </c>
       <c r="U73" s="100" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANTANDER</t>
+          <t xml:space="preserve">Voucher Banco Estado</t>
         </is>
       </c>
       <c r="V73" s="55"/>
     </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="L74" s="49"/>
       <c r="M74" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve">CLIENTE DOS</t>
         </is>
       </c>
-      <c r="U74" s="89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BCI</t>
-        </is>
-      </c>
+      <c r="N74" s="90"/>
+      <c r="O74" s="147"/>
       <c r="P74" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve">F002</t>
         </is>
       </c>
+      <c r="Q74" s="60"/>
+      <c r="R74" s="177"/>
+      <c r="S74" s="177"/>
       <c r="T74" s="69">
         <v>250000</v>
       </c>
+      <c r="U74" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Banco Santander</t>
+        </is>
+      </c>
+      <c r="V74" s="55"/>
     </row>
     <row r="75" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="L75" s="49"/>
-      <c r="M75" s="89"/>
-      <c r="N75" s="90"/>
-      <c r="O75" s="147"/>
-      <c r="P75" s="91"/>
-      <c r="Q75" s="60"/>
-      <c r="R75" s="224"/>
-      <c r="S75" s="224"/>
-      <c r="T75" s="69"/>
-      <c r="U75" s="100"/>
+      <c r="M75" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="N75" s="164"/>
+      <c r="O75" s="165"/>
+      <c r="P75" s="166"/>
+      <c r="Q75" s="167"/>
+      <c r="R75" s="178"/>
+      <c r="S75" s="178"/>
+      <c r="T75" s="175"/>
+      <c r="U75" s="176"/>
       <c r="V75" s="55"/>
     </row>
     <row r="76" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="L76" s="49"/>
       <c r="M76" s="163" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N76" s="164"/>
       <c r="O76" s="165"/>
       <c r="P76" s="166"/>
       <c r="Q76" s="167"/>
-      <c r="R76" s="225"/>
-      <c r="S76" s="225"/>
-      <c r="T76" s="222"/>
-      <c r="U76" s="223"/>
+      <c r="R76" s="168"/>
+      <c r="S76" s="168"/>
+      <c r="T76" s="175"/>
+      <c r="U76" s="176"/>
       <c r="V76" s="55"/>
     </row>
-    <row r="77" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L77" s="49"/>
-      <c r="M77" s="163" t="s">
-        <v>62</v>
-      </c>
-      <c r="N77" s="164"/>
-      <c r="O77" s="165"/>
-      <c r="P77" s="166"/>
-      <c r="Q77" s="167"/>
-      <c r="R77" s="168"/>
-      <c r="S77" s="168"/>
-      <c r="T77" s="222"/>
-      <c r="U77" s="223"/>
+      <c r="M77" s="99"/>
+      <c r="N77" s="68"/>
+      <c r="O77" s="147"/>
+      <c r="P77" s="91"/>
+      <c r="Q77" s="60"/>
+      <c r="R77" s="60"/>
+      <c r="S77" s="60"/>
+      <c r="T77" s="69"/>
+      <c r="U77" s="100"/>
       <c r="V77" s="55"/>
     </row>
     <row r="78" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L78" s="49"/>
-      <c r="M78" s="99"/>
-      <c r="N78" s="68"/>
-      <c r="O78" s="147"/>
-      <c r="P78" s="91"/>
-      <c r="Q78" s="60"/>
-      <c r="R78" s="60"/>
-      <c r="S78" s="60"/>
-      <c r="T78" s="69"/>
-      <c r="U78" s="100"/>
+      <c r="M78" s="106" t="s">
+        <v>11</v>
+      </c>
+      <c r="N78" s="107">
+        <f>SUM(N76:N77)</f>
+        <v>0</v>
+      </c>
+      <c r="O78" s="101"/>
+      <c r="P78" s="103"/>
+      <c r="Q78" s="102"/>
+      <c r="R78" s="102"/>
+      <c r="S78" s="102"/>
+      <c r="T78" s="104"/>
+      <c r="U78" s="105"/>
       <c r="V78" s="55"/>
     </row>
-    <row r="79" spans="1:23" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="L79" s="49"/>
-      <c r="M79" s="106" t="s">
-        <v>11</v>
-      </c>
-      <c r="N79" s="107">
-        <f>SUM(N77:N78)</f>
-        <v>0</v>
-      </c>
-      <c r="O79" s="101"/>
-      <c r="P79" s="103"/>
-      <c r="Q79" s="102"/>
-      <c r="R79" s="102"/>
-      <c r="S79" s="102"/>
-      <c r="T79" s="104"/>
-      <c r="U79" s="105"/>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="M79"/>
+      <c r="O79" s="5"/>
+      <c r="Q79"/>
+      <c r="S79"/>
+      <c r="T79" s="6"/>
       <c r="V79" s="55"/>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="M80"/>
-      <c r="O80" s="5"/>
-      <c r="Q80"/>
-      <c r="S80"/>
-      <c r="T80" s="6"/>
+      <c r="O80"/>
       <c r="V80" s="55"/>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="O81"/>
+    <row r="81" spans="13:22" x14ac:dyDescent="0.3">
+      <c r="M81" s="23"/>
+      <c r="N81" s="23"/>
+      <c r="O81" s="23"/>
+      <c r="P81" s="23"/>
+      <c r="Q81" s="23"/>
       <c r="V81" s="55"/>
     </row>
     <row r="82" spans="13:22" x14ac:dyDescent="0.3">
-      <c r="M82" s="23"/>
-      <c r="N82" s="23"/>
-      <c r="O82" s="23"/>
-      <c r="P82" s="23"/>
-      <c r="Q82" s="23"/>
       <c r="V82" s="55"/>
     </row>
     <row r="83" spans="13:22" x14ac:dyDescent="0.3">
@@ -4125,7 +4158,7 @@
     <row r="96" spans="13:22" x14ac:dyDescent="0.3">
       <c r="V96" s="55"/>
     </row>
-    <row r="97" spans="13:22" x14ac:dyDescent="0.3">
+    <row r="97" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V97" s="55"/>
     </row>
     <row r="98" spans="22:22" x14ac:dyDescent="0.3">
@@ -4173,77 +4206,8 @@
     <row r="112" spans="22:22" x14ac:dyDescent="0.3">
       <c r="V112" s="55"/>
     </row>
-    <row r="113" spans="22:22" x14ac:dyDescent="0.3">
-      <c r="V113" s="55"/>
-    </row>
   </sheetData>
-  <mergeCells count="81">
-    <mergeCell ref="T77:U77"/>
-    <mergeCell ref="R75:S75"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="R76:S76"/>
-    <mergeCell ref="R71:S71"/>
-    <mergeCell ref="R73:S73"/>
-    <mergeCell ref="R72:S72"/>
-    <mergeCell ref="T76:U76"/>
-    <mergeCell ref="M65:N65"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="T67:U67"/>
-    <mergeCell ref="M69:U69"/>
-    <mergeCell ref="R67:S67"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="M67:O67"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="T30:U30"/>
-    <mergeCell ref="Q32:S32"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="R35:S35"/>
-    <mergeCell ref="T35:U35"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:S33"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:S34"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="T25:U25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q25:S25"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:S30"/>
-    <mergeCell ref="B10:D10"/>
+  <mergeCells count="72">
     <mergeCell ref="M22:U22"/>
     <mergeCell ref="Q26:S26"/>
     <mergeCell ref="O29:P29"/>
@@ -4259,6 +4223,63 @@
     <mergeCell ref="T27:U27"/>
     <mergeCell ref="N23:S23"/>
     <mergeCell ref="N24:S24"/>
+    <mergeCell ref="T25:U25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:S25"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:S30"/>
+    <mergeCell ref="T30:U30"/>
+    <mergeCell ref="Q32:S32"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="R35:S35"/>
+    <mergeCell ref="T35:U35"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:S34"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="T67:U67"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="M67:O67"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="T76:U76"/>
+    <mergeCell ref="R74:S74"/>
+    <mergeCell ref="R75:S75"/>
+    <mergeCell ref="R71:S71"/>
+    <mergeCell ref="R73:S73"/>
+    <mergeCell ref="R72:S72"/>
+    <mergeCell ref="T75:U75"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="M69:U69"/>
+    <mergeCell ref="R67:S67"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="D70:E70"/>
   </mergeCells>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0" bottom="0.15748031496062992" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
